--- a/assets/documents/Tableau de synthese - Epreuve E5 - BTS SIO 2026.xlsx
+++ b/assets/documents/Tableau de synthese - Epreuve E5 - BTS SIO 2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="47">
   <si>
     <t xml:space="preserve">BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -150,9 +150,6 @@
   </si>
   <si>
     <t xml:space="preserve">Réalisations en milieu professionnel en cours de première année</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stage chez Orange (Lannion)</t>
   </si>
   <si>
     <t xml:space="preserve">Stage chez LTC </t>
@@ -1174,9 +1171,7 @@
       <c r="G8" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>26</v>
-      </c>
+      <c r="H8" s="17"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -1390,15 +1385,17 @@
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="27"/>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -1419,14 +1416,24 @@
       <c r="Z14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="27"/>
+      <c r="A15" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="30"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -1446,15 +1453,17 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="27"/>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -1475,14 +1484,18 @@
       <c r="Z16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="27"/>
+      <c r="A17" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="30"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -1502,17 +1515,25 @@
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
-        <v>36</v>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
+        <v>40</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="B18" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="30"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -1534,19 +1555,21 @@
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="17" t="s">
+      <c r="B19" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="H19" s="30"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
@@ -1568,23 +1591,21 @@
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="29" t="s">
-        <v>26</v>
+      <c r="B20" s="31" t="s">
+        <v>39</v>
       </c>
+      <c r="C20" s="29"/>
       <c r="D20" s="29"/>
-      <c r="E20" s="29" t="s">
-        <v>26</v>
-      </c>
+      <c r="E20" s="29"/>
       <c r="F20" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="29"/>
+      <c r="H20" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="30"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -1604,17 +1625,23 @@
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="s">
+    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="30" t="s">
+        <v>26</v>
+      </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -1636,17 +1663,23 @@
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="29"/>
       <c r="D22" s="29"/>
       <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="30"/>
+      <c r="F22" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>26</v>
+      </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -1668,23 +1701,21 @@
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
-      <c r="C23" s="29" t="s">
-        <v>26</v>
-      </c>
+      <c r="C23" s="29"/>
       <c r="D23" s="29"/>
       <c r="E23" s="29"/>
-      <c r="F23" s="29" t="s">
-        <v>26</v>
-      </c>
+      <c r="F23" s="29"/>
       <c r="G23" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="30"/>
+      <c r="H23" s="30" t="s">
+        <v>26</v>
+      </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -1705,22 +1736,20 @@
       <c r="Z23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>42</v>
+      <c r="A24" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="30"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
@@ -1740,23 +1769,15 @@
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="29"/>
-      <c r="H25" s="30" t="s">
-        <v>26</v>
-      </c>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="35"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -1776,177 +1797,55 @@
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
-      <c r="Y27" s="4"/>
-      <c r="Z27" s="4"/>
-    </row>
-    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
-      <c r="Z28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-      <c r="Z29" s="4"/>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
@@ -11538,56 +11437,11 @@
       <c r="G989" s="4"/>
       <c r="H989" s="4"/>
     </row>
-    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A990" s="4"/>
-      <c r="B990" s="4"/>
-      <c r="C990" s="4"/>
-      <c r="D990" s="4"/>
-      <c r="E990" s="4"/>
-      <c r="F990" s="4"/>
-      <c r="G990" s="4"/>
-      <c r="H990" s="4"/>
-    </row>
-    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A991" s="4"/>
-      <c r="B991" s="4"/>
-      <c r="C991" s="4"/>
-      <c r="D991" s="4"/>
-      <c r="E991" s="4"/>
-      <c r="F991" s="4"/>
-      <c r="G991" s="4"/>
-      <c r="H991" s="4"/>
-    </row>
-    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A992" s="4"/>
-      <c r="B992" s="4"/>
-      <c r="C992" s="4"/>
-      <c r="D992" s="4"/>
-      <c r="E992" s="4"/>
-      <c r="F992" s="4"/>
-      <c r="G992" s="4"/>
-      <c r="H992" s="4"/>
-    </row>
-    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A993" s="4"/>
-      <c r="B993" s="4"/>
-      <c r="C993" s="4"/>
-      <c r="D993" s="4"/>
-      <c r="E993" s="4"/>
-      <c r="F993" s="4"/>
-      <c r="G993" s="4"/>
-      <c r="H993" s="4"/>
-    </row>
-    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A994" s="4"/>
-      <c r="B994" s="4"/>
-      <c r="C994" s="4"/>
-      <c r="D994" s="4"/>
-      <c r="E994" s="4"/>
-      <c r="F994" s="4"/>
-      <c r="G994" s="4"/>
-      <c r="H994" s="4"/>
-    </row>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -11605,8 +11459,8 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A16:H16"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
